--- a/documentos/Sprint_Backlog_Martech.xlsx
+++ b/documentos/Sprint_Backlog_Martech.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="180">
   <si>
     <t>ID Tarea</t>
   </si>
@@ -457,91 +457,82 @@
     <t>Incorporar selectores de rangos de fechas, comparativas temporales e indicadores de tendencia.</t>
   </si>
   <si>
-    <t>T14-2</t>
-  </si>
-  <si>
-    <t>Configurar y validar la funcionalidad de exportación de informes personalizados a formato PDF y CSV.</t>
+    <t>T16-3</t>
+  </si>
+  <si>
+    <t>Desarrollar modelos Gold de atribución entre campañas y comportamiento web</t>
+  </si>
+  <si>
+    <t>T17-2</t>
+  </si>
+  <si>
+    <t>Desplegar pipelines y vistas de preparación para el tenant AATN</t>
+  </si>
+  <si>
+    <t>T17-3</t>
+  </si>
+  <si>
+    <t>Desplegar pipelines y vistas de preparación para el tenant MC</t>
+  </si>
+  <si>
+    <t>T17-4</t>
+  </si>
+  <si>
+    <t>Validar aislamiento de datos y habilitar el tablero del nuevo tenant</t>
+  </si>
+  <si>
+    <t>QA / BI Developer</t>
+  </si>
+  <si>
+    <t>T18-3</t>
+  </si>
+  <si>
+    <t>Validar integridad referencial del histórico consolidado</t>
+  </si>
+  <si>
+    <t>T19-1</t>
+  </si>
+  <si>
+    <t>PB19</t>
+  </si>
+  <si>
+    <t>HU-19</t>
+  </si>
+  <si>
+    <t>Construir las consultas de contraste entre la plataforma y las fuentes de origen</t>
+  </si>
+  <si>
+    <t>T19-2</t>
+  </si>
+  <si>
+    <t>Ejecutar la auditoría por tenant y documentar las diferencias detectadas</t>
+  </si>
+  <si>
+    <t>T19-3</t>
+  </si>
+  <si>
+    <t>Corregir y reprocesar los períodos con discrepancia no explicada</t>
+  </si>
+  <si>
+    <t>TC-1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Marcha blanca: operación supervisada del pipeline con los 3 tenants</t>
   </si>
   <si>
     <t>En proceso</t>
   </si>
   <si>
-    <t>T16-3</t>
-  </si>
-  <si>
-    <t>Desarrollar modelos Gold de atribución entre campañas y comportamiento web</t>
-  </si>
-  <si>
-    <t>En validación</t>
-  </si>
-  <si>
-    <t>T17-2</t>
-  </si>
-  <si>
-    <t>Desplegar pipelines y vistas de preparación para el tenant AATN</t>
-  </si>
-  <si>
-    <t>T17-3</t>
-  </si>
-  <si>
-    <t>Desplegar pipelines y vistas de preparación para el tenant MC</t>
-  </si>
-  <si>
-    <t>T17-4</t>
-  </si>
-  <si>
-    <t>Validar aislamiento de datos y habilitar el tablero del nuevo tenant</t>
-  </si>
-  <si>
-    <t>QA / BI Developer</t>
-  </si>
-  <si>
-    <t>T18-3</t>
-  </si>
-  <si>
-    <t>Validar integridad referencial del histórico consolidado</t>
-  </si>
-  <si>
-    <t>T19-1</t>
-  </si>
-  <si>
-    <t>PB19</t>
-  </si>
-  <si>
-    <t>HU-19</t>
-  </si>
-  <si>
-    <t>Construir las consultas de contraste entre la plataforma y las fuentes de origen</t>
-  </si>
-  <si>
-    <t>T19-2</t>
-  </si>
-  <si>
-    <t>Ejecutar la auditoría por tenant y documentar las diferencias detectadas</t>
-  </si>
-  <si>
-    <t>T19-3</t>
-  </si>
-  <si>
-    <t>Corregir y reprocesar los períodos con discrepancia no explicada</t>
+    <t>TC-2</t>
+  </si>
+  <si>
+    <t>Registro y corrección de incidencias detectadas en marcha blanca</t>
   </si>
   <si>
     <t>Pendiente</t>
-  </si>
-  <si>
-    <t>TC-1</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Marcha blanca: operación supervisada del pipeline con los 3 tenants</t>
-  </si>
-  <si>
-    <t>TC-2</t>
-  </si>
-  <si>
-    <t>Registro y corrección de incidencias detectadas en marcha blanca</t>
   </si>
   <si>
     <t>TC-3</t>
@@ -646,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -700,9 +691,6 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -851,7 +839,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B49:H68" displayName="Sprint_3" name="Sprint_3" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B49:H67" displayName="Sprint_3" name="Sprint_3" id="4">
   <tableColumns count="7">
     <tableColumn name="ID Tarea" id="1"/>
     <tableColumn name="Backlog ID" id="2"/>
@@ -866,7 +854,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B72:H78" displayName="Cierre" name="Cierre" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B71:H77" displayName="Cierre" name="Cierre" id="5">
   <tableColumns count="7">
     <tableColumn name="ID Tarea" id="1"/>
     <tableColumn name="Backlog ID" id="2"/>
@@ -2376,22 +2364,22 @@
         <v>148</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>149</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="G59" s="5">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
@@ -2399,25 +2387,25 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="B60" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="F60" s="5" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G60" s="5">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
@@ -2425,7 +2413,7 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="B61" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>59</v>
@@ -2434,7 +2422,7 @@
         <v>60</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>11</v>
@@ -2445,13 +2433,11 @@
       <c r="H61" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
+      <c r="J61" s="18"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="B62" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>59</v>
@@ -2460,13 +2446,13 @@
         <v>60</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="G62" s="5">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>12</v>
@@ -2474,19 +2460,19 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="B63" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="F63" s="5" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="G63" s="5">
         <v>10.0</v>
@@ -2497,25 +2483,25 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="B64" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="G64" s="5">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
@@ -2523,254 +2509,233 @@
         <v>163</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="F65" s="5" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="G65" s="5">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="B66" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" s="9">
+        <f>SUM(G50:G66)</f>
+        <v>272</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="18"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="B71" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="B72" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G66" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" ht="22.5" customHeight="1">
-      <c r="B67" s="14" t="s">
+      <c r="D72" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="F72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="68" ht="22.5" customHeight="1">
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" s="9">
-        <f>SUM(G50:G67)</f>
-        <v>282</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="J68" s="18"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" ht="22.5" customHeight="1">
-      <c r="B72" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="B73" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G73" s="5">
-        <v>40.0</v>
+        <v>32.0</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="B74" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="G74" s="5">
-        <v>32.0</v>
+        <v>20.0</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="B75" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="G75" s="5">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="B76" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G76" s="5">
-        <v>24.0</v>
+        <v>16.0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
-      <c r="B77" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1">
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="9" t="s">
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G78" s="9">
-        <f>SUM(G73:G77)</f>
+      <c r="G77" s="9">
+        <f>SUM(G72:G76)</f>
         <v>132</v>
       </c>
-      <c r="H78" s="19"/>
+      <c r="H77" s="10" t="s">
+        <v>170</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="H30:H47 H50:H68">
+    <dataValidation type="list" allowBlank="1" sqref="H30:H47 H50:H67">
       <formula1>"Pendiente,En proceso,En validación,Terminado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H6:H14 H17:H27 H73:H78">
+    <dataValidation type="list" allowBlank="1" sqref="H6:H14 H17:H27 H72:H77">
       <formula1>"Terminado,Pendiente,En validación,En proceso"</formula1>
     </dataValidation>
   </dataValidations>
